--- a/src/utils/cadastro_func.xlsx
+++ b/src/utils/cadastro_func.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="52">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -170,6 +170,12 @@
   </si>
   <si>
     <t xml:space="preserve">000638D8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rua Jose Jorge Abrahao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jardim Dora</t>
   </si>
 </sst>
 </file>
@@ -324,8 +330,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:J22"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="50.35"/>
@@ -1007,6 +1013,38 @@
         <v>49</v>
       </c>
     </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="0" t="n">
+        <v>495</v>
+      </c>
+      <c r="D22" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="0" t="n">
+        <v>12301331</v>
+      </c>
+      <c r="H22" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="0" t="n">
+        <v>32896</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
